--- a/sitepreview/ddcc/ValueSet-DDCCDevicePropertyValueSet.xlsx
+++ b/sitepreview/ddcc/ValueSet-DDCCDevicePropertyValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T09:23:49+00:00</t>
+    <t>2024-10-17T05:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/ddcc/ValueSet-DDCCDevicePropertyValueSet.xlsx
+++ b/sitepreview/ddcc/ValueSet-DDCCDevicePropertyValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T05:11:29+00:00</t>
+    <t>2024-10-17T05:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/ddcc/ValueSet-DDCCDevicePropertyValueSet.xlsx
+++ b/sitepreview/ddcc/ValueSet-DDCCDevicePropertyValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T05:29:58+00:00</t>
+    <t>2024-10-17T06:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
